--- a/artfynd/A 31847-2023 artfynd.xlsx
+++ b/artfynd/A 31847-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133130218</v>
+        <v>133130209</v>
       </c>
       <c r="B2" t="n">
-        <v>57252</v>
+        <v>81031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100038</v>
+        <v>6444</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Skriftlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Graphis scripta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -752,17 +751,13 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>rop från NV</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,38 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133130162</v>
+        <v>133130218</v>
       </c>
       <c r="B3" t="n">
-        <v>103427</v>
+        <v>57269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223246</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,13 +815,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434794</v>
+        <v>434702</v>
       </c>
       <c r="R3" t="n">
-        <v>6212965</v>
+        <v>6213004</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,13 +853,17 @@
           <t>2026-05-05</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>rop från NV</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,6 +879,414 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133130143</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99531</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219878</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Storrams</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Polygonatum multiflorum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hallaröd NO Ullstorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>434794</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6212965</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Önnestad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133130173</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104882</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220461</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsbräsma</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cardamine flexuosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>With.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hallaröd NO Ullstorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>434823</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6212903</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Önnestad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133130147</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104197</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221987</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsbingel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Mercurialis perennis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hallaröd NO Ullstorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>434794</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6212965</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Önnestad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133130162</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103482</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hallaröd NO Ullstorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>434794</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6212965</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Önnestad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31847-2023 artfynd.xlsx
+++ b/artfynd/A 31847-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133130209</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133130218</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133130143</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133130173</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133130147</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,8 +1317,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133130162</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>